--- a/testdata/justgiving_example.xlsx
+++ b/testdata/justgiving_example.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="256" uniqueCount="188">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="256" uniqueCount="187">
   <si>
     <t xml:space="preserve">Fundraiser User Id</t>
   </si>
@@ -582,9 +582,6 @@
   </si>
   <si>
     <t xml:space="preserve">Sum of Net Total Charges By JustGiving</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Vintners Place</t>
   </si>
   <si>
     <t xml:space="preserve">(empty)</t>
@@ -600,7 +597,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="5">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -630,12 +627,6 @@
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <charset val="1"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
     </font>
   </fonts>
   <fills count="3">
@@ -784,21 +775,21 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
     </xf>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
     </xf>
   </cellStyleXfs>
@@ -807,59 +798,59 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="23" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="22" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="22" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="20" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="3" xfId="22" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="3" xfId="20" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="4" xfId="22" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="4" xfId="20" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="5" xfId="21" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="5" xfId="25" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="6" xfId="21" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="6" xfId="25" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="7" xfId="22" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="7" xfId="20" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="8" xfId="21" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="8" xfId="25" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="9" xfId="21" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="9" xfId="25" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="10" xfId="21" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="10" xfId="25" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="11" xfId="21" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="11" xfId="25" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -867,11 +858,11 @@
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="13" xfId="25" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="13" xfId="23" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="14" xfId="25" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="14" xfId="23" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -883,12 +874,12 @@
     <cellStyle name="Currency" xfId="17" builtinId="4"/>
     <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
     <cellStyle name="Percent" xfId="19" builtinId="5"/>
-    <cellStyle name="Pivot Table Corner" xfId="20"/>
-    <cellStyle name="Pivot Table Value" xfId="21"/>
-    <cellStyle name="Pivot Table Category" xfId="22"/>
-    <cellStyle name="Pivot Table Field" xfId="23"/>
+    <cellStyle name="Pivot Table Category" xfId="20"/>
+    <cellStyle name="Pivot Table Corner" xfId="21"/>
+    <cellStyle name="Pivot Table Field" xfId="22"/>
+    <cellStyle name="Pivot Table Result" xfId="23"/>
     <cellStyle name="Pivot Table Title" xfId="24"/>
-    <cellStyle name="Pivot Table Result" xfId="25"/>
+    <cellStyle name="Pivot Table Value" xfId="25"/>
   </cellStyles>
   <dxfs count="3">
     <dxf>
@@ -930,8 +921,8 @@
   <cacheFields count="114">
     <cacheField name="Fundraiser User Id" numFmtId="0">
       <sharedItems containsBlank="1" count="3">
-        <s v="76527572"/>
-        <s v="77062034"/>
+        <s v="7706203456"/>
+        <s v="7706203468"/>
         <m/>
       </sharedItems>
     </cacheField>
@@ -955,13 +946,13 @@
     </cacheField>
     <cacheField name="Fundraiser Address Line 1" numFmtId="0">
       <sharedItems containsBlank="1" count="2">
-        <s v="CBRE"/>
+        <s v="A generous sponsor"/>
         <m/>
       </sharedItems>
     </cacheField>
     <cacheField name="Fundraiser Address Line 2" numFmtId="0">
       <sharedItems containsBlank="1" count="2">
-        <s v="Vintners Place, 68 Upper Thames Street"/>
+        <s v="1 Southampton Row"/>
         <m/>
       </sharedItems>
     </cacheField>
@@ -1139,7 +1130,7 @@
     </cacheField>
     <cacheField name="Event Name" numFmtId="0">
       <sharedItems containsBlank="1" count="3">
-        <s v="Christmas Raffle"/>
+        <s v="Christmas Event"/>
         <s v="Just Fundraising"/>
         <m/>
       </sharedItems>
@@ -1171,21 +1162,22 @@
     </cacheField>
     <cacheField name="Event Date" numFmtId="0">
       <sharedItems containsBlank="1" count="3">
-        <s v="24/11/2025"/>
-        <s v="28/11/2025"/>
+        <s v="24/10/2025"/>
+        <s v="28/10/2025"/>
         <m/>
       </sharedItems>
     </cacheField>
     <cacheField name="Event Expiry Date" numFmtId="0">
       <sharedItems containsBlank="1" count="3">
-        <s v="12/12/2025"/>
-        <s v="27/05/2026"/>
+        <s v="12/1/2025"/>
+        <s v="27/11/2026"/>
         <m/>
       </sharedItems>
     </cacheField>
     <cacheField name="Donor User Id" numFmtId="0">
-      <sharedItems containsBlank="1" count="2">
-        <s v="65086821"/>
+      <sharedItems containsBlank="1" count="3">
+        <s v="990868212"/>
+        <s v="990868223"/>
         <m/>
       </sharedItems>
     </cacheField>
@@ -1268,15 +1260,15 @@
     </cacheField>
     <cacheField name="Donation Ref" numFmtId="0">
       <sharedItems containsBlank="1" count="3">
-        <s v="565653315"/>
-        <s v="827239094"/>
+        <s v="989777889"/>
+        <s v="989777890"/>
         <m/>
       </sharedItems>
     </cacheField>
     <cacheField name="Donation Date" numFmtId="0">
       <sharedItems containsBlank="1" count="3">
-        <s v="04/12/2025"/>
-        <s v="08/12/2025"/>
+        <s v="04/11/2025"/>
+        <s v="08/11/2025"/>
         <m/>
       </sharedItems>
     </cacheField>
@@ -1311,7 +1303,7 @@
     </cacheField>
     <cacheField name="Appeal Name" numFmtId="0">
       <sharedItems containsBlank="1" count="2">
-        <s v="Rays of Sunshine Children's Charity: General Appeal"/>
+        <s v="A Charity’s General Appeal"/>
         <m/>
       </sharedItems>
     </cacheField>
@@ -1506,7 +1498,7 @@
     <cacheField name="Custom Fundraising 3" numFmtId="0">
       <sharedItems containsBlank="1" count="3">
         <s v="Corporate"/>
-        <s v="Vintners Place"/>
+        <s v="Southampton Row"/>
         <m/>
       </sharedItems>
     </cacheField>
@@ -1550,8 +1542,8 @@
     </cacheField>
     <cacheField name="Fundraiser Page Consent Date" numFmtId="0">
       <sharedItems containsBlank="1" count="3">
-        <s v="2025-11-13 12:38:55"/>
-        <s v="2025-11-28 11:16:57"/>
+        <s v="2025-10-13 12:38:55"/>
+        <s v="2025-10-28 11:16:57"/>
         <m/>
       </sharedItems>
     </cacheField>
@@ -1575,8 +1567,8 @@
     </cacheField>
     <cacheField name="Donation Consent Date" numFmtId="0">
       <sharedItems containsBlank="1" count="3">
-        <s v="2025-12-04 10:07:15"/>
-        <s v="2025-12-08 18:11:31"/>
+        <s v="2025-11-04 10:07:15"/>
+        <s v="2025-11-08 18:11:31"/>
         <m/>
       </sharedItems>
     </cacheField>
@@ -1617,7 +1609,7 @@
 <file path=xl/pivotCache/pivotCacheRecords1.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" count="2">
   <r>
-    <x v="1"/>
+    <x v="0"/>
     <x v="0"/>
     <x v="0"/>
     <x v="0"/>
@@ -1733,7 +1725,7 @@
     <x v="0"/>
   </r>
   <r>
-    <x v="0"/>
+    <x v="1"/>
     <x v="0"/>
     <x v="0"/>
     <x v="1"/>
@@ -1775,7 +1767,7 @@
     <x v="0"/>
     <x v="0"/>
     <x v="0"/>
-    <x v="0"/>
+    <x v="1"/>
     <x v="0"/>
     <x v="0"/>
     <x v="0"/>
@@ -1954,8 +1946,8 @@
     <pivotField axis="axisRow" showAll="0">
       <items count="4">
         <item x="0"/>
+        <item x="2"/>
         <item x="1"/>
-        <item x="2"/>
         <item t="default"/>
       </items>
     </pivotField>
@@ -2190,961 +2182,961 @@
   <dimension ref="A1:DJ3"/>
   <sheetFormatPr defaultColWidth="10.16015625" defaultRowHeight="14.25" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="19.52"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="16.95"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="22.1"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="21.85"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="5" style="0" width="25.9"/>
-    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="7" min="7" style="0" width="18.06"/>
-    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="8" min="8" style="0" width="19.4"/>
-    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="9" min="9" style="0" width="21.12"/>
-    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="10" min="10" style="0" width="20.13"/>
-    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="11" min="11" style="0" width="29.94"/>
-    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="12" min="12" style="0" width="26.51"/>
-    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="13" min="13" style="0" width="28.84"/>
-    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="14" min="14" style="0" width="20.75"/>
-    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="15" min="15" style="0" width="24.18"/>
-    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="16" min="16" style="0" width="19.4"/>
-    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="17" min="17" style="0" width="17.56"/>
-    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="18" min="18" style="0" width="18.17"/>
-    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="19" min="19" style="0" width="32.15"/>
-    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="20" min="20" style="0" width="31.78"/>
-    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="21" min="21" style="0" width="40.6"/>
-    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="22" min="22" style="0" width="60.22"/>
-    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="23" min="23" style="0" width="29.21"/>
-    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="24" min="24" style="0" width="27.61"/>
-    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="25" min="25" style="0" width="32.27"/>
-    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="26" min="26" style="0" width="20.26"/>
-    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="27" min="27" style="0" width="20.38"/>
-    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="28" min="28" style="0" width="24.3"/>
-    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="29" min="29" style="0" width="36.19"/>
-    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="30" min="30" style="0" width="31.78"/>
-    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="31" min="31" style="0" width="33.01"/>
-    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="32" min="32" style="0" width="25.53"/>
-    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="33" min="33" style="0" width="14.62"/>
-    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="34" min="34" style="0" width="17.93"/>
-    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="35" min="35" style="0" width="10.7"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="36" min="36" style="0" width="15.11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="37" min="37" style="0" width="17.44"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="38" min="38" style="0" width="20.02"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="39" min="39" style="0" width="22.7"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="40" min="40" style="0" width="16.82"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="41" min="41" style="0" width="12.9"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="42" min="42" style="0" width="18.67"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="43" min="43" style="0" width="15.85"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="44" min="44" style="0" width="13.27"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="45" min="45" style="0" width="18.42"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="46" min="46" style="0" width="18.17"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="48" min="47" style="0" width="22.22"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="49" min="49" style="0" width="14.37"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="50" min="50" style="0" width="15.72"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="51" min="51" style="0" width="17.44"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="52" min="52" style="0" width="16.46"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="53" min="53" style="0" width="14.98"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="54" min="54" style="0" width="22.83"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="55" min="55" style="0" width="20.63"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="56" min="56" style="0" width="26.51"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="57" min="57" style="0" width="14.87"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="58" min="58" style="0" width="16.09"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="59" min="59" style="0" width="11.55"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="60" min="60" style="0" width="17.93"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="61" min="61" style="0" width="16.71"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="62" min="62" style="0" width="20.63"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="63" min="63" style="0" width="32.02"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="64" min="64" style="0" width="45.02"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="65" min="65" style="0" width="18.29"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="66" min="66" style="0" width="15.72"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="67" min="67" style="0" width="35.33"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="68" min="68" style="0" width="28.47"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="69" min="69" style="0" width="32.88"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="72" min="70" style="0" width="16.82"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="73" min="73" style="0" width="19.03"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="74" min="74" style="0" width="23.33"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="75" min="75" style="0" width="28.59"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="76" min="76" style="0" width="31.78"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="77" min="77" style="0" width="35.33"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="78" min="78" style="0" width="36.44"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="79" min="79" style="0" width="30.31"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="80" min="80" style="0" width="33.49"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="81" min="81" style="0" width="22.47"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="82" min="82" style="0" width="15.97"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="83" min="83" style="0" width="40.24"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="84" min="84" style="0" width="38.52"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="85" min="85" style="0" width="19.64"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="86" min="86" style="0" width="30.56"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="87" min="87" style="0" width="26.64"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="88" min="88" style="0" width="17.56"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="89" min="89" style="0" width="20.63"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="90" min="90" style="0" width="21.85"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="91" min="91" style="0" width="20.5"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="94" min="92" style="0" width="21.85"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="100" min="95" style="0" width="22.47"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="103" min="101" style="0" width="18.79"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="104" min="104" style="0" width="24.91"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="105" min="105" style="0" width="29.33"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="106" min="106" style="0" width="36.93"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="107" min="107" style="0" width="33.98"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="108" min="108" style="0" width="19.03"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="109" min="109" style="0" width="23.45"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="110" min="110" style="0" width="32.15"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="111" min="111" style="0" width="28.1"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="112" min="112" style="0" width="29.08"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="113" min="113" style="0" width="45.75"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="114" min="114" style="0" width="67.33"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="19.52"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="16.95"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="22.1"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="21.85"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="5" style="1" width="25.9"/>
+    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="7" min="7" style="1" width="18.07"/>
+    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="8" min="8" style="1" width="19.4"/>
+    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="9" min="9" style="1" width="21.12"/>
+    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="10" min="10" style="1" width="20.13"/>
+    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="11" min="11" style="1" width="29.93"/>
+    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="12" min="12" style="1" width="26.51"/>
+    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="13" min="13" style="1" width="28.84"/>
+    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="14" min="14" style="1" width="20.76"/>
+    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="15" min="15" style="1" width="24.18"/>
+    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="16" min="16" style="1" width="19.4"/>
+    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="17" min="17" style="1" width="17.56"/>
+    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="18" min="18" style="1" width="18.17"/>
+    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="19" min="19" style="1" width="32.15"/>
+    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="20" min="20" style="1" width="31.78"/>
+    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="21" min="21" style="1" width="40.6"/>
+    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="22" min="22" style="1" width="60.22"/>
+    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="23" min="23" style="1" width="29.21"/>
+    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="24" min="24" style="1" width="27.61"/>
+    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="25" min="25" style="1" width="32.27"/>
+    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="26" min="26" style="1" width="20.26"/>
+    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="27" min="27" style="1" width="20.38"/>
+    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="28" min="28" style="1" width="24.3"/>
+    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="29" min="29" style="1" width="36.19"/>
+    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="30" min="30" style="1" width="31.78"/>
+    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="31" min="31" style="1" width="33.01"/>
+    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="32" min="32" style="1" width="25.53"/>
+    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="33" min="33" style="1" width="14.62"/>
+    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="34" min="34" style="1" width="17.93"/>
+    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="35" min="35" style="1" width="10.7"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="36" min="36" style="1" width="15.11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="37" min="37" style="1" width="17.44"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="38" min="38" style="1" width="20.02"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="39" min="39" style="1" width="22.7"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="40" min="40" style="1" width="16.82"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="41" min="41" style="1" width="12.9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="42" min="42" style="1" width="18.67"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="43" min="43" style="1" width="15.85"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="44" min="44" style="1" width="13.27"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="45" min="45" style="1" width="18.42"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="46" min="46" style="1" width="18.17"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="48" min="47" style="1" width="22.22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="49" min="49" style="1" width="14.37"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="50" min="50" style="1" width="15.72"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="51" min="51" style="1" width="17.44"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="52" min="52" style="1" width="16.46"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="53" min="53" style="1" width="14.97"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="54" min="54" style="1" width="22.83"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="55" min="55" style="1" width="20.63"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="56" min="56" style="1" width="26.51"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="57" min="57" style="1" width="14.88"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="58" min="58" style="1" width="16.09"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="59" min="59" style="1" width="11.55"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="60" min="60" style="1" width="17.93"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="61" min="61" style="1" width="16.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="62" min="62" style="1" width="20.63"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="63" min="63" style="1" width="32.02"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="64" min="64" style="1" width="45.03"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="65" min="65" style="1" width="18.29"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="66" min="66" style="1" width="15.72"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="67" min="67" style="1" width="35.33"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="68" min="68" style="1" width="28.47"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="69" min="69" style="1" width="32.88"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="72" min="70" style="1" width="16.82"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="73" min="73" style="1" width="19.03"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="74" min="74" style="1" width="23.33"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="75" min="75" style="1" width="28.59"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="76" min="76" style="1" width="31.78"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="77" min="77" style="1" width="35.33"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="78" min="78" style="1" width="36.44"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="79" min="79" style="1" width="30.31"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="80" min="80" style="1" width="33.49"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="81" min="81" style="1" width="22.47"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="82" min="82" style="1" width="15.97"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="83" min="83" style="1" width="40.24"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="84" min="84" style="1" width="38.52"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="85" min="85" style="1" width="19.64"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="86" min="86" style="1" width="30.56"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="87" min="87" style="1" width="26.64"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="88" min="88" style="1" width="17.56"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="89" min="89" style="1" width="20.63"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="90" min="90" style="1" width="21.85"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="91" min="91" style="1" width="20.5"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="94" min="92" style="1" width="21.85"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="100" min="95" style="1" width="22.47"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="103" min="101" style="1" width="18.79"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="104" min="104" style="1" width="24.91"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="105" min="105" style="1" width="29.33"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="106" min="106" style="1" width="36.93"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="107" min="107" style="1" width="33.98"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="108" min="108" style="1" width="19.03"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="109" min="109" style="1" width="23.45"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="110" min="110" style="1" width="32.15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="111" min="111" style="1" width="28.1"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="112" min="112" style="1" width="29.08"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="113" min="113" style="1" width="45.75"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="114" min="114" style="1" width="67.33"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="K1" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="L1" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="M1" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="N1" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="O1" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="P1" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="Q1" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="1" t="s">
+      <c r="R1" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="1" t="s">
+      <c r="S1" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="T1" s="1" t="s">
+      <c r="T1" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="U1" s="1" t="s">
+      <c r="U1" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="V1" s="1" t="s">
+      <c r="V1" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="W1" s="1" t="s">
+      <c r="W1" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="X1" s="1" t="s">
+      <c r="X1" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="Y1" s="1" t="s">
+      <c r="Y1" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="Z1" s="1" t="s">
+      <c r="Z1" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AA1" s="1" t="s">
+      <c r="AA1" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="AB1" s="1" t="s">
+      <c r="AB1" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="AC1" s="1" t="s">
+      <c r="AC1" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="AD1" s="1" t="s">
+      <c r="AD1" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="AE1" s="1" t="s">
+      <c r="AE1" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="AF1" s="1" t="s">
+      <c r="AF1" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="AG1" s="1" t="s">
+      <c r="AG1" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="AH1" s="1" t="s">
+      <c r="AH1" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="AI1" s="1" t="s">
+      <c r="AI1" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="AJ1" s="2" t="s">
+      <c r="AJ1" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="AK1" s="1" t="s">
+      <c r="AK1" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="AL1" s="1" t="s">
+      <c r="AL1" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="AM1" s="1" t="s">
+      <c r="AM1" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="AN1" s="1" t="s">
+      <c r="AN1" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="AO1" s="1" t="s">
+      <c r="AO1" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="AP1" s="1" t="s">
+      <c r="AP1" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="AQ1" s="1" t="s">
+      <c r="AQ1" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="AR1" s="1" t="s">
+      <c r="AR1" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="AS1" s="1" t="s">
+      <c r="AS1" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="AT1" s="1" t="s">
+      <c r="AT1" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="AU1" s="1" t="s">
+      <c r="AU1" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="AV1" s="1" t="s">
+      <c r="AV1" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="AW1" s="1" t="s">
+      <c r="AW1" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="AX1" s="1" t="s">
+      <c r="AX1" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="AY1" s="1" t="s">
+      <c r="AY1" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="AZ1" s="1" t="s">
+      <c r="AZ1" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="BA1" s="1" t="s">
+      <c r="BA1" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="BB1" s="1" t="s">
+      <c r="BB1" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="BC1" s="1" t="s">
+      <c r="BC1" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="BD1" s="1" t="s">
+      <c r="BD1" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="BE1" s="1" t="s">
+      <c r="BE1" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="BF1" s="1" t="s">
+      <c r="BF1" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="BG1" s="1" t="s">
+      <c r="BG1" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="BH1" s="1" t="s">
+      <c r="BH1" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="BI1" s="1" t="s">
+      <c r="BI1" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="BJ1" s="2" t="s">
+      <c r="BJ1" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="BK1" s="1" t="s">
+      <c r="BK1" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="BL1" s="1" t="s">
+      <c r="BL1" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="BM1" s="1" t="s">
+      <c r="BM1" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="BN1" s="1" t="s">
+      <c r="BN1" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="BO1" s="1" t="s">
+      <c r="BO1" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="BP1" s="1" t="s">
+      <c r="BP1" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="BQ1" s="1" t="s">
+      <c r="BQ1" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="BR1" s="1" t="s">
+      <c r="BR1" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="BS1" s="1" t="s">
+      <c r="BS1" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="BT1" s="1" t="s">
+      <c r="BT1" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="BU1" s="2" t="s">
+      <c r="BU1" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="BV1" s="1" t="s">
+      <c r="BV1" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="BW1" s="1" t="s">
+      <c r="BW1" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="BX1" s="1" t="s">
+      <c r="BX1" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="BY1" s="1" t="s">
+      <c r="BY1" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="BZ1" s="1" t="s">
+      <c r="BZ1" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="CA1" s="1" t="s">
+      <c r="CA1" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="CB1" s="1" t="s">
+      <c r="CB1" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="CC1" s="1" t="s">
+      <c r="CC1" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="CD1" s="1" t="s">
+      <c r="CD1" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="CE1" s="1" t="s">
+      <c r="CE1" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="CF1" s="1" t="s">
+      <c r="CF1" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="CG1" s="1" t="s">
+      <c r="CG1" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="CH1" s="2" t="s">
+      <c r="CH1" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="CI1" s="1" t="s">
+      <c r="CI1" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="CJ1" s="1" t="s">
+      <c r="CJ1" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="CK1" s="1" t="s">
+      <c r="CK1" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="CL1" s="1" t="s">
+      <c r="CL1" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="CM1" s="1" t="s">
+      <c r="CM1" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="CN1" s="1" t="s">
+      <c r="CN1" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="CO1" s="1" t="s">
+      <c r="CO1" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="CP1" s="1" t="s">
+      <c r="CP1" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="CQ1" s="1" t="s">
+      <c r="CQ1" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="CR1" s="1" t="s">
+      <c r="CR1" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="CS1" s="2" t="s">
+      <c r="CS1" s="3" t="s">
         <v>96</v>
       </c>
-      <c r="CT1" s="1" t="s">
+      <c r="CT1" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="CU1" s="1" t="s">
+      <c r="CU1" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="CV1" s="1" t="s">
+      <c r="CV1" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="CW1" s="1" t="s">
+      <c r="CW1" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="CX1" s="1" t="s">
+      <c r="CX1" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="CY1" s="1" t="s">
+      <c r="CY1" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="CZ1" s="1" t="s">
+      <c r="CZ1" s="2" t="s">
         <v>103</v>
       </c>
-      <c r="DA1" s="1" t="s">
+      <c r="DA1" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="DB1" s="1" t="s">
+      <c r="DB1" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="DC1" s="1" t="s">
+      <c r="DC1" s="2" t="s">
         <v>106</v>
       </c>
-      <c r="DD1" s="1" t="s">
+      <c r="DD1" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="DE1" s="1" t="s">
+      <c r="DE1" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="DF1" s="1" t="s">
+      <c r="DF1" s="2" t="s">
         <v>109</v>
       </c>
-      <c r="DG1" s="1" t="s">
+      <c r="DG1" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="DH1" s="1" t="s">
+      <c r="DH1" s="2" t="s">
         <v>111</v>
       </c>
-      <c r="DI1" s="1" t="s">
+      <c r="DI1" s="2" t="s">
         <v>112</v>
       </c>
-      <c r="DJ1" s="1" t="s">
+      <c r="DJ1" s="2" t="s">
         <v>113</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="s">
+      <c r="A2" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="C2" s="0" t="s">
+      <c r="C2" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="D2" s="0" t="s">
+      <c r="D2" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="K2" s="0" t="s">
+      <c r="K2" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="L2" s="0" t="s">
+      <c r="L2" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="M2" s="0" t="s">
+      <c r="M2" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="N2" s="0" t="s">
+      <c r="N2" s="1" t="s">
         <v>119</v>
       </c>
-      <c r="O2" s="0" t="s">
+      <c r="O2" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="P2" s="0" t="s">
+      <c r="P2" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="Q2" s="0" t="s">
+      <c r="Q2" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="R2" s="0" t="s">
+      <c r="R2" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="S2" s="0" t="n">
+      <c r="S2" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="T2" s="0" t="n">
+      <c r="T2" s="1" t="n">
         <v>500</v>
       </c>
-      <c r="U2" s="0" t="s">
+      <c r="U2" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="V2" s="0" t="s">
+      <c r="V2" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="Z2" s="0" t="s">
+      <c r="Z2" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="AG2" s="0" t="s">
+      <c r="AG2" s="1" t="s">
         <v>125</v>
       </c>
-      <c r="AI2" s="0" t="s">
+      <c r="AI2" s="1" t="s">
         <v>119</v>
       </c>
-      <c r="AJ2" s="0" t="s">
+      <c r="AJ2" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="AK2" s="0" t="s">
+      <c r="AK2" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="AL2" s="0" t="s">
+      <c r="AL2" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="AM2" s="0" t="s">
+      <c r="AM2" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="AN2" s="0" t="s">
+      <c r="AN2" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="AO2" s="0" t="s">
+      <c r="AO2" s="1" t="s">
         <v>129</v>
       </c>
-      <c r="AP2" s="0" t="s">
+      <c r="AP2" s="1" t="s">
         <v>130</v>
       </c>
-      <c r="AQ2" s="0" t="s">
+      <c r="AQ2" s="1" t="s">
         <v>131</v>
       </c>
-      <c r="AR2" s="0" t="s">
+      <c r="AR2" s="1" t="s">
         <v>132</v>
       </c>
-      <c r="AS2" s="0" t="s">
+      <c r="AS2" s="1" t="s">
         <v>132</v>
       </c>
-      <c r="AT2" s="0" t="s">
+      <c r="AT2" s="1" t="s">
         <v>132</v>
       </c>
-      <c r="AU2" s="0" t="s">
+      <c r="AU2" s="1" t="s">
         <v>132</v>
       </c>
-      <c r="AV2" s="0" t="s">
+      <c r="AV2" s="1" t="s">
         <v>132</v>
       </c>
-      <c r="AW2" s="0" t="s">
+      <c r="AW2" s="1" t="s">
         <v>132</v>
       </c>
-      <c r="AX2" s="0" t="s">
+      <c r="AX2" s="1" t="s">
         <v>132</v>
       </c>
-      <c r="AY2" s="0" t="s">
+      <c r="AY2" s="1" t="s">
         <v>132</v>
       </c>
-      <c r="BA2" s="0" t="s">
+      <c r="BA2" s="1" t="s">
         <v>132</v>
       </c>
-      <c r="BB2" s="0" t="s">
+      <c r="BB2" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="BC2" s="0" t="s">
+      <c r="BC2" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="BD2" s="0" t="s">
+      <c r="BD2" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="BE2" s="0" t="s">
+      <c r="BE2" s="1" t="s">
         <v>133</v>
       </c>
-      <c r="BF2" s="0" t="s">
+      <c r="BF2" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="BG2" s="0" t="s">
+      <c r="BG2" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="BH2" s="0" t="s">
+      <c r="BH2" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="BI2" s="0" t="s">
+      <c r="BI2" s="1" t="s">
         <v>136</v>
       </c>
-      <c r="BJ2" s="0" t="s">
+      <c r="BJ2" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="BL2" s="0" t="s">
+      <c r="BL2" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="BM2" s="0" t="s">
+      <c r="BM2" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="BO2" s="0" t="n">
+      <c r="BO2" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="BP2" s="0" t="n">
+      <c r="BP2" s="1" t="n">
         <v>4877124</v>
       </c>
-      <c r="BQ2" s="0" t="s">
+      <c r="BQ2" s="1" t="s">
         <v>140</v>
       </c>
-      <c r="BU2" s="0" t="n">
+      <c r="BU2" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="BV2" s="0" t="s">
+      <c r="BV2" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="BW2" s="0" t="s">
+      <c r="BW2" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="BX2" s="0" t="n">
+      <c r="BX2" s="1" t="n">
         <v>0.19</v>
       </c>
-      <c r="BY2" s="0" t="n">
+      <c r="BY2" s="1" t="n">
         <v>0.3</v>
       </c>
-      <c r="BZ2" s="0" t="n">
+      <c r="BZ2" s="1" t="n">
         <v>0.49</v>
       </c>
-      <c r="CA2" s="0" t="s">
+      <c r="CA2" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="CB2" s="0" t="n">
+      <c r="CB2" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="CC2" s="0" t="n">
+      <c r="CC2" s="1" t="n">
         <v>9.51</v>
       </c>
-      <c r="CD2" s="0" t="n">
+      <c r="CD2" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="CE2" s="0" t="n">
+      <c r="CE2" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="CF2" s="0" t="n">
+      <c r="CF2" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="CG2" s="0" t="s">
+      <c r="CG2" s="1" t="s">
         <v>143</v>
       </c>
-      <c r="CH2" s="0" t="n">
+      <c r="CH2" s="1" t="n">
         <v>0.49</v>
       </c>
-      <c r="CI2" s="0" t="n">
+      <c r="CI2" s="1" t="n">
         <v>9.51</v>
       </c>
-      <c r="CJ2" s="0" t="s">
+      <c r="CJ2" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="CK2" s="0" t="s">
+      <c r="CK2" s="1" t="s">
         <v>145</v>
       </c>
-      <c r="CM2" s="0" t="s">
+      <c r="CM2" s="1" t="s">
         <v>146</v>
       </c>
-      <c r="CQ2" s="0" t="s">
+      <c r="CQ2" s="1" t="s">
         <v>147</v>
       </c>
-      <c r="CR2" s="0" t="s">
+      <c r="CR2" s="1" t="s">
         <v>148</v>
       </c>
-      <c r="CS2" s="0" t="s">
+      <c r="CS2" s="1" t="s">
         <v>149</v>
       </c>
-      <c r="CT2" s="0" t="s">
+      <c r="CT2" s="1" t="s">
         <v>150</v>
       </c>
-      <c r="CU2" s="0" t="s">
+      <c r="CU2" s="1" t="s">
         <v>151</v>
       </c>
-      <c r="CZ2" s="0" t="s">
+      <c r="CZ2" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="DA2" s="0" t="s">
+      <c r="DA2" s="1" t="s">
         <v>152</v>
       </c>
-      <c r="DB2" s="0" t="s">
+      <c r="DB2" s="1" t="s">
         <v>153</v>
       </c>
-      <c r="DC2" s="0" t="s">
+      <c r="DC2" s="1" t="s">
         <v>154</v>
       </c>
-      <c r="DD2" s="0" t="s">
+      <c r="DD2" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="DE2" s="0" t="s">
+      <c r="DE2" s="1" t="s">
         <v>155</v>
       </c>
-      <c r="DF2" s="0" t="s">
+      <c r="DF2" s="1" t="s">
         <v>153</v>
       </c>
-      <c r="DG2" s="0" t="s">
+      <c r="DG2" s="1" t="s">
         <v>154</v>
       </c>
-      <c r="DH2" s="0" t="s">
+      <c r="DH2" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="DI2" s="0" t="n">
+      <c r="DI2" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="DJ2" s="0" t="n">
+      <c r="DJ2" s="1" t="n">
         <v>12.5</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="s">
+      <c r="A3" s="1" t="s">
         <v>156</v>
       </c>
-      <c r="C3" s="0" t="s">
+      <c r="C3" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="D3" s="0" t="s">
+      <c r="D3" s="1" t="s">
         <v>157</v>
       </c>
-      <c r="E3" s="0" t="s">
+      <c r="E3" s="1" t="s">
         <v>158</v>
       </c>
-      <c r="F3" s="0" t="s">
+      <c r="F3" s="1" t="s">
         <v>159</v>
       </c>
-      <c r="G3" s="0" t="s">
+      <c r="G3" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="I3" s="0" t="s">
+      <c r="I3" s="1" t="s">
         <v>161</v>
       </c>
-      <c r="J3" s="0" t="s">
+      <c r="J3" s="1" t="s">
         <v>162</v>
       </c>
-      <c r="K3" s="0" t="s">
+      <c r="K3" s="1" t="s">
         <v>163</v>
       </c>
-      <c r="L3" s="0" t="s">
+      <c r="L3" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="M3" s="0" t="s">
+      <c r="M3" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="N3" s="0" t="s">
+      <c r="N3" s="1" t="s">
         <v>164</v>
       </c>
-      <c r="O3" s="0" t="s">
+      <c r="O3" s="1" t="s">
         <v>165</v>
       </c>
-      <c r="P3" s="0" t="s">
+      <c r="P3" s="1" t="s">
         <v>166</v>
       </c>
-      <c r="Q3" s="0" t="s">
+      <c r="Q3" s="1" t="s">
         <v>167</v>
       </c>
-      <c r="R3" s="0" t="s">
+      <c r="R3" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="S3" s="0" t="n">
+      <c r="S3" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="T3" s="0" t="n">
+      <c r="T3" s="1" t="n">
         <v>500</v>
       </c>
-      <c r="U3" s="0" t="s">
+      <c r="U3" s="1" t="s">
         <v>169</v>
       </c>
-      <c r="V3" s="0" t="s">
+      <c r="V3" s="1" t="s">
         <v>170</v>
       </c>
-      <c r="Z3" s="0" t="s">
+      <c r="Z3" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="AG3" s="0" t="s">
+      <c r="AG3" s="1" t="s">
         <v>125</v>
       </c>
-      <c r="AI3" s="0" t="s">
+      <c r="AI3" s="1" t="s">
         <v>164</v>
       </c>
-      <c r="AJ3" s="0" t="s">
+      <c r="AJ3" s="1" t="s">
         <v>171</v>
       </c>
-      <c r="AK3" s="0" t="s">
+      <c r="AK3" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="AL3" s="0" t="s">
+      <c r="AL3" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="AM3" s="0" t="s">
+      <c r="AM3" s="1" t="s">
         <v>172</v>
       </c>
-      <c r="AN3" s="0" t="s">
+      <c r="AN3" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="AO3" s="0" t="s">
+      <c r="AO3" s="1" t="s">
         <v>173</v>
       </c>
-      <c r="AP3" s="0" t="s">
+      <c r="AP3" s="1" t="s">
         <v>174</v>
       </c>
-      <c r="AQ3" s="0" t="s">
+      <c r="AQ3" s="1" t="s">
         <v>175</v>
       </c>
-      <c r="AR3" s="0" t="s">
+      <c r="AR3" s="1" t="s">
         <v>132</v>
       </c>
-      <c r="AS3" s="0" t="s">
+      <c r="AS3" s="1" t="s">
         <v>132</v>
       </c>
-      <c r="AT3" s="0" t="s">
+      <c r="AT3" s="1" t="s">
         <v>132</v>
       </c>
-      <c r="AU3" s="0" t="s">
+      <c r="AU3" s="1" t="s">
         <v>132</v>
       </c>
-      <c r="AV3" s="0" t="s">
+      <c r="AV3" s="1" t="s">
         <v>132</v>
       </c>
-      <c r="AW3" s="0" t="s">
+      <c r="AW3" s="1" t="s">
         <v>132</v>
       </c>
-      <c r="AX3" s="0" t="s">
+      <c r="AX3" s="1" t="s">
         <v>132</v>
       </c>
-      <c r="AY3" s="0" t="s">
+      <c r="AY3" s="1" t="s">
         <v>132</v>
       </c>
-      <c r="BA3" s="0" t="s">
+      <c r="BA3" s="1" t="s">
         <v>132</v>
       </c>
-      <c r="BB3" s="0" t="s">
+      <c r="BB3" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="BC3" s="0" t="s">
+      <c r="BC3" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="BD3" s="0" t="s">
+      <c r="BD3" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="BE3" s="3" t="s">
+      <c r="BE3" s="2" t="s">
         <v>176</v>
       </c>
-      <c r="BF3" s="0" t="s">
+      <c r="BF3" s="1" t="s">
         <v>177</v>
       </c>
-      <c r="BG3" s="0" t="s">
+      <c r="BG3" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="BH3" s="0" t="s">
+      <c r="BH3" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="BI3" s="0" t="s">
+      <c r="BI3" s="1" t="s">
         <v>136</v>
       </c>
-      <c r="BJ3" s="0" t="s">
+      <c r="BJ3" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="BL3" s="0" t="s">
+      <c r="BL3" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="BM3" s="0" t="s">
+      <c r="BM3" s="1" t="s">
         <v>178</v>
       </c>
-      <c r="BO3" s="0" t="n">
+      <c r="BO3" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="BP3" s="0" t="n">
+      <c r="BP3" s="1" t="n">
         <v>4877123</v>
       </c>
-      <c r="BQ3" s="0" t="s">
+      <c r="BQ3" s="1" t="s">
         <v>140</v>
       </c>
-      <c r="BU3" s="0" t="n">
+      <c r="BU3" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="BV3" s="0" t="s">
+      <c r="BV3" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="BW3" s="0" t="s">
+      <c r="BW3" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="BX3" s="0" t="n">
+      <c r="BX3" s="1" t="n">
         <v>0.19</v>
       </c>
-      <c r="BY3" s="0" t="n">
+      <c r="BY3" s="1" t="n">
         <v>0.3</v>
       </c>
-      <c r="BZ3" s="0" t="n">
+      <c r="BZ3" s="1" t="n">
         <v>0.49</v>
       </c>
-      <c r="CA3" s="0" t="s">
+      <c r="CA3" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="CB3" s="0" t="n">
+      <c r="CB3" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="CC3" s="0" t="n">
+      <c r="CC3" s="1" t="n">
         <v>9.51</v>
       </c>
-      <c r="CD3" s="0" t="n">
+      <c r="CD3" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="CE3" s="0" t="n">
+      <c r="CE3" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="CF3" s="0" t="n">
+      <c r="CF3" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="CG3" s="0" t="s">
+      <c r="CG3" s="1" t="s">
         <v>143</v>
       </c>
-      <c r="CH3" s="0" t="n">
+      <c r="CH3" s="1" t="n">
         <v>0.49</v>
       </c>
-      <c r="CI3" s="0" t="n">
+      <c r="CI3" s="1" t="n">
         <v>9.51</v>
       </c>
-      <c r="CJ3" s="0" t="s">
+      <c r="CJ3" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="CM3" s="0" t="s">
+      <c r="CM3" s="1" t="s">
         <v>179</v>
       </c>
-      <c r="CQ3" s="0" t="s">
+      <c r="CQ3" s="1" t="s">
         <v>147</v>
       </c>
-      <c r="CR3" s="0" t="s">
+      <c r="CR3" s="1" t="s">
         <v>149</v>
       </c>
-      <c r="CS3" s="0" t="s">
+      <c r="CS3" s="1" t="s">
         <v>180</v>
       </c>
-      <c r="CT3" s="0" t="s">
+      <c r="CT3" s="1" t="s">
         <v>150</v>
       </c>
-      <c r="CZ3" s="0" t="s">
+      <c r="CZ3" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="DA3" s="0" t="s">
+      <c r="DA3" s="1" t="s">
         <v>181</v>
       </c>
-      <c r="DB3" s="0" t="s">
+      <c r="DB3" s="1" t="s">
         <v>153</v>
       </c>
-      <c r="DC3" s="0" t="s">
+      <c r="DC3" s="1" t="s">
         <v>154</v>
       </c>
-      <c r="DD3" s="0" t="s">
+      <c r="DD3" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="DE3" s="0" t="s">
+      <c r="DE3" s="1" t="s">
         <v>182</v>
       </c>
-      <c r="DF3" s="0" t="s">
+      <c r="DF3" s="1" t="s">
         <v>153</v>
       </c>
-      <c r="DG3" s="0" t="s">
+      <c r="DG3" s="1" t="s">
         <v>154</v>
       </c>
-      <c r="DH3" s="0" t="s">
+      <c r="DH3" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="DI3" s="0" t="n">
+      <c r="DI3" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="DJ3" s="0" t="n">
+      <c r="DJ3" s="1" t="n">
         <v>12.5</v>
       </c>
     </row>
@@ -3169,10 +3161,10 @@
   <dimension ref="A3:C15"/>
   <sheetFormatPr defaultColWidth="8.59765625" defaultRowHeight="14.25" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="17.78"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="21.44"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="32.78"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="21.44"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="17.78"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="21.44"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="32.78"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="21.44"/>
   </cols>
   <sheetData>
     <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3201,23 +3193,23 @@
       <c r="A5" s="10" t="s">
         <v>185</v>
       </c>
-      <c r="B5" s="11" t="n">
-        <v>10</v>
-      </c>
-      <c r="C5" s="12" t="n">
-        <v>0.49</v>
-      </c>
+      <c r="B5" s="11"/>
+      <c r="C5" s="12"/>
     </row>
     <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="10" t="s">
-        <v>186</v>
-      </c>
-      <c r="B6" s="13"/>
-      <c r="C6" s="14"/>
+        <v>180</v>
+      </c>
+      <c r="B6" s="13" t="n">
+        <v>10</v>
+      </c>
+      <c r="C6" s="14" t="n">
+        <v>0.49</v>
+      </c>
     </row>
     <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="15" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B7" s="16" t="n">
         <v>20</v>
@@ -3227,7 +3219,7 @@
       </c>
     </row>
     <row r="15" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B15" s="0" t="n">
+      <c r="B15" s="1" t="n">
         <f aca="false">GETPIVOTDATA("Sum of Donation Amount",$A$3,"Custom Fundraising 3","Corporate")+GETPIVOTDATA("Sum of Donation Amount",$A$3,"Custom Fundraising 3","General (not Appeal)")+GETPIVOTDATA("Sum of Donation Amount",$A$3,"Custom Fundraising 3","Vintners Place")</f>
         <v>2264.52</v>
       </c>
